--- a/outputs/v0/02_trending_output.xlsx
+++ b/outputs/v0/02_trending_output.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Student Stats" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Stats" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overall" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assessment Stats" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z-Scores" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overall" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:V26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,65 +427,105 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>test1</t>
+          <t>quiz_1</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>test2</t>
+          <t>quiz_2</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>test3</t>
+          <t>quiz_3</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>test4</t>
+          <t>quiz_4</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>test5</t>
+          <t>test_1</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>test_2</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>test_3</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>test_4</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>test_5</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>test_6</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>simple_average</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>weighted_average</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>letter_grade</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>slope</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>std_dev</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>highest_score</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>lowest_score</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>percentile</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>z_score</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
         <is>
           <t>above_class_average</t>
         </is>
@@ -497,45 +538,69 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C2" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D2" t="n">
+        <v>57</v>
+      </c>
+      <c r="E2" t="n">
         <v>70</v>
       </c>
-      <c r="E2" t="n">
-        <v>80</v>
-      </c>
       <c r="F2" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="G2" t="n">
-        <v>70</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>C-</t>
-        </is>
+        <v>72</v>
+      </c>
+      <c r="H2" t="n">
+        <v>76</v>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="J2" t="n">
-        <v>15.811388</v>
+        <v>84</v>
       </c>
       <c r="K2" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L2" t="n">
-        <v>50</v>
+        <v>71.2</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N2" t="b">
-        <v>1</v>
+        <v>75.016667</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>3.781818</v>
+      </c>
+      <c r="P2" t="n">
+        <v>11.726513</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>87</v>
+      </c>
+      <c r="R2" t="n">
+        <v>53</v>
+      </c>
+      <c r="S2" t="n">
+        <v>16</v>
+      </c>
+      <c r="T2" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="V2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -545,44 +610,68 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="C3" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="D3" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F3" t="n">
+        <v>72</v>
+      </c>
+      <c r="G3" t="n">
+        <v>73</v>
+      </c>
+      <c r="H3" t="n">
+        <v>78</v>
+      </c>
+      <c r="I3" t="n">
+        <v>84</v>
+      </c>
+      <c r="J3" t="n">
+        <v>86</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86</v>
+      </c>
+      <c r="L3" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>76.516667</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>3.284848</v>
+      </c>
+      <c r="P3" t="n">
+        <v>10.042133</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>86</v>
+      </c>
+      <c r="R3" t="n">
+        <v>59</v>
+      </c>
+      <c r="S3" t="n">
+        <v>12</v>
+      </c>
+      <c r="T3" t="n">
         <v>50</v>
       </c>
-      <c r="G3" t="n">
-        <v>70</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>C-</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J3" t="n">
-        <v>15.811388</v>
-      </c>
-      <c r="K3" t="n">
-        <v>90</v>
-      </c>
-      <c r="L3" t="n">
-        <v>50</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2</v>
-      </c>
-      <c r="N3" t="b">
+      <c r="U3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -593,44 +682,68 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C4" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D4" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E4" t="n">
+        <v>70</v>
+      </c>
+      <c r="F4" t="n">
+        <v>76</v>
+      </c>
+      <c r="G4" t="n">
+        <v>83</v>
+      </c>
+      <c r="H4" t="n">
         <v>79</v>
       </c>
-      <c r="F4" t="n">
-        <v>88</v>
-      </c>
-      <c r="G4" t="n">
-        <v>71</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>C-</t>
-        </is>
-      </c>
       <c r="I4" t="n">
-        <v>8.300000000000001</v>
+        <v>89</v>
       </c>
       <c r="J4" t="n">
-        <v>13.133926</v>
+        <v>85</v>
       </c>
       <c r="K4" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="L4" t="n">
-        <v>55</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="b">
+        <v>80.283333</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>3.660606</v>
+      </c>
+      <c r="P4" t="n">
+        <v>11.432896</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>93</v>
+      </c>
+      <c r="R4" t="n">
+        <v>58</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="V4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -641,45 +754,69 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="C5" t="n">
+        <v>69</v>
+      </c>
+      <c r="D5" t="n">
+        <v>71</v>
+      </c>
+      <c r="E5" t="n">
         <v>75</v>
       </c>
-      <c r="D5" t="n">
-        <v>65</v>
-      </c>
-      <c r="E5" t="n">
-        <v>55</v>
-      </c>
       <c r="F5" t="n">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="G5" t="n">
-        <v>65.59999999999999</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
+        <v>81</v>
+      </c>
+      <c r="H5" t="n">
+        <v>81</v>
       </c>
       <c r="I5" t="n">
-        <v>-10.6</v>
+        <v>85</v>
       </c>
       <c r="J5" t="n">
-        <v>16.7869</v>
+        <v>92</v>
       </c>
       <c r="K5" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="L5" t="n">
-        <v>45</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="M5" t="n">
+        <v>81.466667</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>3.739394</v>
+      </c>
+      <c r="P5" t="n">
+        <v>11.685223</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>97</v>
+      </c>
+      <c r="R5" t="n">
+        <v>57</v>
+      </c>
+      <c r="S5" t="n">
         <v>4</v>
       </c>
-      <c r="N5" t="b">
-        <v>0</v>
+      <c r="T5" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="V5" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -689,44 +826,1508 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>64</v>
+      </c>
+      <c r="C6" t="n">
+        <v>65</v>
+      </c>
+      <c r="D6" t="n">
+        <v>68</v>
+      </c>
+      <c r="E6" t="n">
+        <v>78</v>
+      </c>
+      <c r="F6" t="n">
+        <v>79</v>
+      </c>
+      <c r="G6" t="n">
+        <v>83</v>
+      </c>
+      <c r="H6" t="n">
+        <v>92</v>
+      </c>
+      <c r="I6" t="n">
+        <v>86</v>
+      </c>
+      <c r="J6" t="n">
+        <v>100</v>
+      </c>
+      <c r="K6" t="n">
+        <v>100</v>
+      </c>
+      <c r="L6" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>85.75</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>4.272727</v>
+      </c>
+      <c r="P6" t="n">
+        <v>13.318742</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>100</v>
+      </c>
+      <c r="R6" t="n">
+        <v>64</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>100</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S006</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>70</v>
+      </c>
+      <c r="C7" t="n">
+        <v>71</v>
+      </c>
+      <c r="D7" t="n">
+        <v>70</v>
+      </c>
+      <c r="E7" t="n">
+        <v>79</v>
+      </c>
+      <c r="F7" t="n">
+        <v>78</v>
+      </c>
+      <c r="G7" t="n">
+        <v>83</v>
+      </c>
+      <c r="H7" t="n">
+        <v>86</v>
+      </c>
+      <c r="I7" t="n">
+        <v>92</v>
+      </c>
+      <c r="J7" t="n">
+        <v>98</v>
+      </c>
+      <c r="K7" t="n">
+        <v>96</v>
+      </c>
+      <c r="L7" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>85.566667</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>3.387879</v>
+      </c>
+      <c r="P7" t="n">
+        <v>10.551988</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>98</v>
+      </c>
+      <c r="R7" t="n">
+        <v>70</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>S007</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>85</v>
+      </c>
+      <c r="C8" t="n">
+        <v>81</v>
+      </c>
+      <c r="D8" t="n">
+        <v>78</v>
+      </c>
+      <c r="E8" t="n">
+        <v>73</v>
+      </c>
+      <c r="F8" t="n">
+        <v>71</v>
+      </c>
+      <c r="G8" t="n">
+        <v>74</v>
+      </c>
+      <c r="H8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I8" t="n">
+        <v>63</v>
+      </c>
+      <c r="J8" t="n">
+        <v>55</v>
+      </c>
+      <c r="K8" t="n">
+        <v>56</v>
+      </c>
+      <c r="L8" t="n">
+        <v>70</v>
+      </c>
+      <c r="M8" t="n">
+        <v>66.916667</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>D+</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>-3.284848</v>
+      </c>
+      <c r="P8" t="n">
+        <v>10.230673</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>85</v>
+      </c>
+      <c r="R8" t="n">
+        <v>55</v>
+      </c>
+      <c r="S8" t="n">
+        <v>24</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="V8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>S008</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>85</v>
+      </c>
+      <c r="C9" t="n">
+        <v>84</v>
+      </c>
+      <c r="D9" t="n">
+        <v>89</v>
+      </c>
+      <c r="E9" t="n">
+        <v>77</v>
+      </c>
+      <c r="F9" t="n">
+        <v>79</v>
+      </c>
+      <c r="G9" t="n">
+        <v>73</v>
+      </c>
+      <c r="H9" t="n">
+        <v>68</v>
+      </c>
+      <c r="I9" t="n">
+        <v>62</v>
+      </c>
+      <c r="J9" t="n">
+        <v>65</v>
+      </c>
+      <c r="K9" t="n">
+        <v>56</v>
+      </c>
+      <c r="L9" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="M9" t="n">
+        <v>70.483333</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>-3.406061</v>
+      </c>
+      <c r="P9" t="n">
+        <v>10.881176</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>89</v>
+      </c>
+      <c r="R9" t="n">
+        <v>56</v>
+      </c>
+      <c r="S9" t="n">
+        <v>22</v>
+      </c>
+      <c r="T9" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="V9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>S009</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>97</v>
+      </c>
+      <c r="C10" t="n">
+        <v>86</v>
+      </c>
+      <c r="D10" t="n">
+        <v>85</v>
+      </c>
+      <c r="E10" t="n">
+        <v>82</v>
+      </c>
+      <c r="F10" t="n">
+        <v>78</v>
+      </c>
+      <c r="G10" t="n">
+        <v>70</v>
+      </c>
+      <c r="H10" t="n">
+        <v>68</v>
+      </c>
+      <c r="I10" t="n">
+        <v>66</v>
+      </c>
+      <c r="J10" t="n">
         <v>60</v>
       </c>
-      <c r="C6" t="n">
+      <c r="K10" t="n">
+        <v>61</v>
+      </c>
+      <c r="L10" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>71.233333</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>-3.945455</v>
+      </c>
+      <c r="P10" t="n">
+        <v>12.19335</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>97</v>
+      </c>
+      <c r="R10" t="n">
         <v>60</v>
       </c>
-      <c r="D6" t="n">
-        <v>60</v>
-      </c>
-      <c r="E6" t="n">
-        <v>60</v>
-      </c>
-      <c r="F6" t="n">
-        <v>60</v>
-      </c>
-      <c r="G6" t="n">
-        <v>60</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>D-</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="V10" t="b">
         <v>0</v>
       </c>
-      <c r="J6" t="n">
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>S010</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>96</v>
+      </c>
+      <c r="C11" t="n">
+        <v>84</v>
+      </c>
+      <c r="D11" t="n">
+        <v>81</v>
+      </c>
+      <c r="E11" t="n">
+        <v>79</v>
+      </c>
+      <c r="F11" t="n">
+        <v>80</v>
+      </c>
+      <c r="G11" t="n">
+        <v>82</v>
+      </c>
+      <c r="H11" t="n">
+        <v>71</v>
+      </c>
+      <c r="I11" t="n">
+        <v>69</v>
+      </c>
+      <c r="J11" t="n">
+        <v>61</v>
+      </c>
+      <c r="K11" t="n">
+        <v>58</v>
+      </c>
+      <c r="L11" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="M11" t="n">
+        <v>73.13333299999999</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>-3.545455</v>
+      </c>
+      <c r="P11" t="n">
+        <v>11.415876</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>96</v>
+      </c>
+      <c r="R11" t="n">
+        <v>58</v>
+      </c>
+      <c r="S11" t="n">
+        <v>18</v>
+      </c>
+      <c r="T11" t="n">
+        <v>25</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="V11" t="b">
         <v>0</v>
       </c>
-      <c r="K6" t="n">
-        <v>60</v>
-      </c>
-      <c r="L6" t="n">
-        <v>60</v>
-      </c>
-      <c r="M6" t="n">
-        <v>5</v>
-      </c>
-      <c r="N6" t="b">
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>S011</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>90</v>
+      </c>
+      <c r="C12" t="n">
+        <v>92</v>
+      </c>
+      <c r="D12" t="n">
+        <v>92</v>
+      </c>
+      <c r="E12" t="n">
+        <v>84</v>
+      </c>
+      <c r="F12" t="n">
+        <v>86</v>
+      </c>
+      <c r="G12" t="n">
+        <v>78</v>
+      </c>
+      <c r="H12" t="n">
+        <v>74</v>
+      </c>
+      <c r="I12" t="n">
+        <v>72</v>
+      </c>
+      <c r="J12" t="n">
+        <v>68</v>
+      </c>
+      <c r="K12" t="n">
+        <v>66</v>
+      </c>
+      <c r="L12" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>-3.163636</v>
+      </c>
+      <c r="P12" t="n">
+        <v>9.908469999999999</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>92</v>
+      </c>
+      <c r="R12" t="n">
+        <v>66</v>
+      </c>
+      <c r="S12" t="n">
+        <v>11</v>
+      </c>
+      <c r="T12" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="V12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>S012</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>96</v>
+      </c>
+      <c r="C13" t="n">
+        <v>87</v>
+      </c>
+      <c r="D13" t="n">
+        <v>91</v>
+      </c>
+      <c r="E13" t="n">
+        <v>85</v>
+      </c>
+      <c r="F13" t="n">
+        <v>83</v>
+      </c>
+      <c r="G13" t="n">
+        <v>85</v>
+      </c>
+      <c r="H13" t="n">
+        <v>73</v>
+      </c>
+      <c r="I13" t="n">
+        <v>75</v>
+      </c>
+      <c r="J13" t="n">
+        <v>72</v>
+      </c>
+      <c r="K13" t="n">
+        <v>66</v>
+      </c>
+      <c r="L13" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>78.483333</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>-2.963636</v>
+      </c>
+      <c r="P13" t="n">
+        <v>9.440457</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>96</v>
+      </c>
+      <c r="R13" t="n">
+        <v>66</v>
+      </c>
+      <c r="S13" t="n">
+        <v>8</v>
+      </c>
+      <c r="T13" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="V13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>S013</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>68</v>
+      </c>
+      <c r="C14" t="n">
+        <v>65</v>
+      </c>
+      <c r="D14" t="n">
+        <v>66</v>
+      </c>
+      <c r="E14" t="n">
+        <v>73</v>
+      </c>
+      <c r="F14" t="n">
+        <v>74</v>
+      </c>
+      <c r="G14" t="n">
+        <v>78</v>
+      </c>
+      <c r="H14" t="n">
+        <v>76</v>
+      </c>
+      <c r="I14" t="n">
+        <v>82</v>
+      </c>
+      <c r="J14" t="n">
+        <v>77</v>
+      </c>
+      <c r="K14" t="n">
+        <v>77</v>
+      </c>
+      <c r="L14" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="M14" t="n">
+        <v>75.466667</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>1.563636</v>
+      </c>
+      <c r="P14" t="n">
+        <v>5.601587</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>82</v>
+      </c>
+      <c r="R14" t="n">
+        <v>65</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="V14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>S014</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>61</v>
+      </c>
+      <c r="C15" t="n">
+        <v>65</v>
+      </c>
+      <c r="D15" t="n">
+        <v>73</v>
+      </c>
+      <c r="E15" t="n">
+        <v>68</v>
+      </c>
+      <c r="F15" t="n">
+        <v>72</v>
+      </c>
+      <c r="G15" t="n">
+        <v>82</v>
+      </c>
+      <c r="H15" t="n">
+        <v>80</v>
+      </c>
+      <c r="I15" t="n">
+        <v>84</v>
+      </c>
+      <c r="J15" t="n">
+        <v>77</v>
+      </c>
+      <c r="K15" t="n">
+        <v>75</v>
+      </c>
+      <c r="L15" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="M15" t="n">
+        <v>76.016667</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>1.884848</v>
+      </c>
+      <c r="P15" t="n">
+        <v>7.454305</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>84</v>
+      </c>
+      <c r="R15" t="n">
+        <v>61</v>
+      </c>
+      <c r="S15" t="n">
+        <v>13</v>
+      </c>
+      <c r="T15" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="V15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S015</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>74</v>
+      </c>
+      <c r="C16" t="n">
+        <v>66</v>
+      </c>
+      <c r="D16" t="n">
+        <v>73</v>
+      </c>
+      <c r="E16" t="n">
+        <v>75</v>
+      </c>
+      <c r="F16" t="n">
+        <v>73</v>
+      </c>
+      <c r="G16" t="n">
+        <v>82</v>
+      </c>
+      <c r="H16" t="n">
+        <v>84</v>
+      </c>
+      <c r="I16" t="n">
+        <v>82</v>
+      </c>
+      <c r="J16" t="n">
+        <v>82</v>
+      </c>
+      <c r="K16" t="n">
+        <v>85</v>
+      </c>
+      <c r="L16" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="M16" t="n">
+        <v>79.466667</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>1.769697</v>
+      </c>
+      <c r="P16" t="n">
+        <v>6.239658</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>85</v>
+      </c>
+      <c r="R16" t="n">
+        <v>66</v>
+      </c>
+      <c r="S16" t="n">
+        <v>6</v>
+      </c>
+      <c r="T16" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="V16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>68</v>
+      </c>
+      <c r="C17" t="n">
+        <v>72</v>
+      </c>
+      <c r="D17" t="n">
+        <v>74</v>
+      </c>
+      <c r="E17" t="n">
+        <v>73</v>
+      </c>
+      <c r="F17" t="n">
+        <v>80</v>
+      </c>
+      <c r="G17" t="n">
+        <v>75</v>
+      </c>
+      <c r="H17" t="n">
+        <v>80</v>
+      </c>
+      <c r="I17" t="n">
+        <v>76</v>
+      </c>
+      <c r="J17" t="n">
+        <v>86</v>
+      </c>
+      <c r="K17" t="n">
+        <v>88</v>
+      </c>
+      <c r="L17" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>79.016667</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>1.842424</v>
+      </c>
+      <c r="P17" t="n">
+        <v>6.285786</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>88</v>
+      </c>
+      <c r="R17" t="n">
+        <v>68</v>
+      </c>
+      <c r="S17" t="n">
+        <v>7</v>
+      </c>
+      <c r="T17" t="n">
+        <v>75</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="V17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>S017</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>75</v>
+      </c>
+      <c r="C18" t="n">
+        <v>83</v>
+      </c>
+      <c r="D18" t="n">
+        <v>79</v>
+      </c>
+      <c r="E18" t="n">
+        <v>75</v>
+      </c>
+      <c r="F18" t="n">
+        <v>88</v>
+      </c>
+      <c r="G18" t="n">
+        <v>79</v>
+      </c>
+      <c r="H18" t="n">
+        <v>85</v>
+      </c>
+      <c r="I18" t="n">
+        <v>87</v>
+      </c>
+      <c r="J18" t="n">
+        <v>84</v>
+      </c>
+      <c r="K18" t="n">
+        <v>92</v>
+      </c>
+      <c r="L18" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="M18" t="n">
+        <v>84.266667</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>1.339394</v>
+      </c>
+      <c r="P18" t="n">
+        <v>5.638164</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>92</v>
+      </c>
+      <c r="R18" t="n">
+        <v>75</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>S018</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>81</v>
+      </c>
+      <c r="C19" t="n">
+        <v>80</v>
+      </c>
+      <c r="D19" t="n">
+        <v>75</v>
+      </c>
+      <c r="E19" t="n">
+        <v>79</v>
+      </c>
+      <c r="F19" t="n">
+        <v>71</v>
+      </c>
+      <c r="G19" t="n">
+        <v>66</v>
+      </c>
+      <c r="H19" t="n">
+        <v>74</v>
+      </c>
+      <c r="I19" t="n">
+        <v>67</v>
+      </c>
+      <c r="J19" t="n">
+        <v>67</v>
+      </c>
+      <c r="K19" t="n">
+        <v>71</v>
+      </c>
+      <c r="L19" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="M19" t="n">
+        <v>71.216667</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>-1.460606</v>
+      </c>
+      <c r="P19" t="n">
+        <v>5.606544</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>81</v>
+      </c>
+      <c r="R19" t="n">
+        <v>66</v>
+      </c>
+      <c r="S19" t="n">
+        <v>21</v>
+      </c>
+      <c r="T19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="V19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>S019</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>85</v>
+      </c>
+      <c r="C20" t="n">
+        <v>82</v>
+      </c>
+      <c r="D20" t="n">
+        <v>82</v>
+      </c>
+      <c r="E20" t="n">
+        <v>75</v>
+      </c>
+      <c r="F20" t="n">
+        <v>78</v>
+      </c>
+      <c r="G20" t="n">
+        <v>77</v>
+      </c>
+      <c r="H20" t="n">
+        <v>74</v>
+      </c>
+      <c r="I20" t="n">
+        <v>70</v>
+      </c>
+      <c r="J20" t="n">
+        <v>57</v>
+      </c>
+      <c r="K20" t="n">
+        <v>69</v>
+      </c>
+      <c r="L20" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="M20" t="n">
+        <v>72.86666700000001</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>-2.321212</v>
+      </c>
+      <c r="P20" t="n">
+        <v>8.143846</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>85</v>
+      </c>
+      <c r="R20" t="n">
+        <v>57</v>
+      </c>
+      <c r="S20" t="n">
+        <v>19</v>
+      </c>
+      <c r="T20" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="V20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>S020</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>84</v>
+      </c>
+      <c r="C21" t="n">
+        <v>81</v>
+      </c>
+      <c r="D21" t="n">
+        <v>83</v>
+      </c>
+      <c r="E21" t="n">
+        <v>80</v>
+      </c>
+      <c r="F21" t="n">
+        <v>78</v>
+      </c>
+      <c r="G21" t="n">
+        <v>71</v>
+      </c>
+      <c r="H21" t="n">
+        <v>70</v>
+      </c>
+      <c r="I21" t="n">
+        <v>73</v>
+      </c>
+      <c r="J21" t="n">
+        <v>71</v>
+      </c>
+      <c r="K21" t="n">
+        <v>69</v>
+      </c>
+      <c r="L21" t="n">
+        <v>76</v>
+      </c>
+      <c r="M21" t="n">
+        <v>74</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>-1.769697</v>
+      </c>
+      <c r="P21" t="n">
+        <v>5.792716</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>84</v>
+      </c>
+      <c r="R21" t="n">
+        <v>69</v>
+      </c>
+      <c r="S21" t="n">
+        <v>17</v>
+      </c>
+      <c r="T21" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="V21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>S021</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>86</v>
+      </c>
+      <c r="C22" t="n">
+        <v>86</v>
+      </c>
+      <c r="D22" t="n">
+        <v>83</v>
+      </c>
+      <c r="E22" t="n">
+        <v>81</v>
+      </c>
+      <c r="F22" t="n">
+        <v>80</v>
+      </c>
+      <c r="G22" t="n">
+        <v>80</v>
+      </c>
+      <c r="H22" t="n">
+        <v>74</v>
+      </c>
+      <c r="I22" t="n">
+        <v>77</v>
+      </c>
+      <c r="J22" t="n">
+        <v>75</v>
+      </c>
+      <c r="K22" t="n">
+        <v>71</v>
+      </c>
+      <c r="L22" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="M22" t="n">
+        <v>77.733333</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>-1.593939</v>
+      </c>
+      <c r="P22" t="n">
+        <v>5.034327</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>86</v>
+      </c>
+      <c r="R22" t="n">
+        <v>71</v>
+      </c>
+      <c r="S22" t="n">
+        <v>9</v>
+      </c>
+      <c r="T22" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="V22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>S022</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>87</v>
+      </c>
+      <c r="C23" t="n">
+        <v>87</v>
+      </c>
+      <c r="D23" t="n">
+        <v>87</v>
+      </c>
+      <c r="E23" t="n">
+        <v>80</v>
+      </c>
+      <c r="F23" t="n">
+        <v>82</v>
+      </c>
+      <c r="G23" t="n">
+        <v>80</v>
+      </c>
+      <c r="H23" t="n">
+        <v>76</v>
+      </c>
+      <c r="I23" t="n">
+        <v>74</v>
+      </c>
+      <c r="J23" t="n">
+        <v>70</v>
+      </c>
+      <c r="K23" t="n">
+        <v>70</v>
+      </c>
+      <c r="L23" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="M23" t="n">
+        <v>77.316667</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>-2.127273</v>
+      </c>
+      <c r="P23" t="n">
+        <v>6.650814</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>87</v>
+      </c>
+      <c r="R23" t="n">
+        <v>70</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="V23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>S023</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>64</v>
+      </c>
+      <c r="C24" t="n">
+        <v>68</v>
+      </c>
+      <c r="D24" t="n">
+        <v>68</v>
+      </c>
+      <c r="E24" t="n">
+        <v>68</v>
+      </c>
+      <c r="F24" t="n">
+        <v>71</v>
+      </c>
+      <c r="G24" t="n">
+        <v>69</v>
+      </c>
+      <c r="H24" t="n">
+        <v>67</v>
+      </c>
+      <c r="I24" t="n">
+        <v>67</v>
+      </c>
+      <c r="J24" t="n">
+        <v>65</v>
+      </c>
+      <c r="K24" t="n">
+        <v>69</v>
+      </c>
+      <c r="L24" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="M24" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>D+</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>0.08484800000000001</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.01108</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>71</v>
+      </c>
+      <c r="R24" t="n">
+        <v>64</v>
+      </c>
+      <c r="S24" t="n">
+        <v>23</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-1.74</v>
+      </c>
+      <c r="V24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>S024</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>72</v>
+      </c>
+      <c r="C25" t="n">
+        <v>79</v>
+      </c>
+      <c r="D25" t="n">
+        <v>79</v>
+      </c>
+      <c r="E25" t="n">
+        <v>79</v>
+      </c>
+      <c r="F25" t="n">
+        <v>81</v>
+      </c>
+      <c r="G25" t="n">
+        <v>68</v>
+      </c>
+      <c r="H25" t="n">
+        <v>76</v>
+      </c>
+      <c r="I25" t="n">
+        <v>76</v>
+      </c>
+      <c r="J25" t="n">
+        <v>75</v>
+      </c>
+      <c r="K25" t="n">
+        <v>82</v>
+      </c>
+      <c r="L25" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="M25" t="n">
+        <v>76.516667</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>0.151515</v>
+      </c>
+      <c r="P25" t="n">
+        <v>4.270051</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>82</v>
+      </c>
+      <c r="R25" t="n">
+        <v>68</v>
+      </c>
+      <c r="S25" t="n">
+        <v>12</v>
+      </c>
+      <c r="T25" t="n">
+        <v>50</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>S025</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>86</v>
+      </c>
+      <c r="C26" t="n">
+        <v>80</v>
+      </c>
+      <c r="D26" t="n">
+        <v>79</v>
+      </c>
+      <c r="E26" t="n">
+        <v>72</v>
+      </c>
+      <c r="F26" t="n">
+        <v>72</v>
+      </c>
+      <c r="G26" t="n">
+        <v>79</v>
+      </c>
+      <c r="H26" t="n">
+        <v>76</v>
+      </c>
+      <c r="I26" t="n">
+        <v>71</v>
+      </c>
+      <c r="J26" t="n">
+        <v>76</v>
+      </c>
+      <c r="K26" t="n">
+        <v>77</v>
+      </c>
+      <c r="L26" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="M26" t="n">
+        <v>75.983333</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.787879</v>
+      </c>
+      <c r="P26" t="n">
+        <v>4.54117</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>86</v>
+      </c>
+      <c r="R26" t="n">
+        <v>71</v>
+      </c>
+      <c r="S26" t="n">
+        <v>14</v>
+      </c>
+      <c r="T26" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="V26" t="b">
         <v>0</v>
       </c>
     </row>
@@ -741,13 +2342,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>assessment</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -774,96 +2375,191 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>test1</t>
+          <t>quiz_1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>68.59999999999999</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>18.968395</v>
+        <v>13.371238</v>
       </c>
       <c r="D2" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>test2</t>
+          <t>quiz_2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>67.40000000000001</v>
+        <v>75.95999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>9.423375</v>
+        <v>9.62843</v>
       </c>
       <c r="D3" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>test3</t>
+          <t>quiz_3</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>67.2</v>
+        <v>76.52</v>
       </c>
       <c r="C4" t="n">
-        <v>4.658326</v>
+        <v>9.019054000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="E4" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>test4</t>
+          <t>quiz_4</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>66.8</v>
+        <v>75.92</v>
       </c>
       <c r="C5" t="n">
-        <v>11.777096</v>
+        <v>4.957486</v>
       </c>
       <c r="D5" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E5" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>test5</t>
+          <t>test_1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>66.59999999999999</v>
+        <v>77.08</v>
       </c>
       <c r="C6" t="n">
-        <v>21.161285</v>
+        <v>4.864155</v>
       </c>
       <c r="D6" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E6" t="n">
-        <v>45</v>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>test_2</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>76.92</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5.4461</v>
+      </c>
+      <c r="D7" t="n">
+        <v>85</v>
+      </c>
+      <c r="E7" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>test_3</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>76.08</v>
+      </c>
+      <c r="C8" t="n">
+        <v>6.486653</v>
+      </c>
+      <c r="D8" t="n">
+        <v>92</v>
+      </c>
+      <c r="E8" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>test_4</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>76.44</v>
+      </c>
+      <c r="C9" t="n">
+        <v>8.480763</v>
+      </c>
+      <c r="D9" t="n">
+        <v>92</v>
+      </c>
+      <c r="E9" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>test_5</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>75.52</v>
+      </c>
+      <c r="C10" t="n">
+        <v>12.086908</v>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>test_6</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>76.68000000000001</v>
+      </c>
+      <c r="C11" t="n">
+        <v>13.256194</v>
+      </c>
+      <c r="D11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" t="n">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -877,45 +2573,1039 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>student_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>quiz_1</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>quiz_2</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>quiz_3</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>quiz_4</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>test_1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>test_2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>test_3</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>test_4</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>test_5</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>test_6</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>class_average</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>67.31999999999999</v>
+        <v>-1.72</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-1.76</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.78</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>class_median</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70</v>
+        <v>-1.27</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>S003</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>S004</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-1.42</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>S005</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S006</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>S007</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-1.86</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-1.56</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>S008</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-1.56</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>S009</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-1.18</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>S010</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-1.41</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>S011</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>S012</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>S013</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>S014</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S015</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>S017</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>S018</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-2.01</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>S019</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>S020</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>S021</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>S022</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>S023</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>S024</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-1.64</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>S025</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>class_weighted_average</t>
+        </is>
+      </c>
+      <c r="B1" t="n">
+        <v>76.38466699999999</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>class_median</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>76.516667</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>grade_A+</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>grade_A</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -925,7 +3615,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>grade_A</t>
+          <t>grade_A-</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -935,7 +3625,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>grade_A-</t>
+          <t>grade_B+</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -945,67 +3635,67 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>grade_B+</t>
+          <t>grade_B</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>grade_B</t>
+          <t>grade_B-</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>grade_B-</t>
+          <t>grade_C+</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>grade_C+</t>
+          <t>grade_C</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>grade_C</t>
+          <t>grade_C-</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>grade_C-</t>
+          <t>grade_D+</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>grade_D+</t>
+          <t>grade_D</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1015,54 +3705,44 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>grade_D</t>
+          <t>grade_D-</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>grade_D-</t>
+          <t>grade_F</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>grade_F</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
+          <t>most_improved_student</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S005</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>most_improved_student</t>
+          <t>most_consistent_student</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>S001</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>most_consistent_student</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>S005</t>
+          <t>S023</t>
         </is>
       </c>
     </row>
